--- a/CPRD Raw Analysis/Results/Overall/overall_combined_bootstrap_summary_encounters_SOURCE.xlsx
+++ b/CPRD Raw Analysis/Results/Overall/overall_combined_bootstrap_summary_encounters_SOURCE.xlsx
@@ -1,21 +1,77 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unioxfordnexus-my.sharepoint.com/personal/orms1149_ox_ac_uk/Documents/Documents/GitHub/OMOP-Validation-Study/CPRD Raw Analysis/Results/Overall/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_CC64FDCE8F79A8D366075C52F30722B4E2DEB15C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EDD63BD7-85E7-4282-A3C4-0C42F32AA71B}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="3624" yWindow="3360" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+  <si>
+    <t>group</t>
+  </si>
+  <si>
+    <t>mean</t>
+  </si>
+  <si>
+    <t>variance</t>
+  </si>
+  <si>
+    <t>sd</t>
+  </si>
+  <si>
+    <t>se</t>
+  </si>
+  <si>
+    <t>ci_norm_lower</t>
+  </si>
+  <si>
+    <t>ci_norm_upper</t>
+  </si>
+  <si>
+    <t>ci_basic_lower</t>
+  </si>
+  <si>
+    <t>ci_basic_upper</t>
+  </si>
+  <si>
+    <t>ci_perc_lower</t>
+  </si>
+  <si>
+    <t>ci_perc_upper</t>
+  </si>
+  <si>
+    <t>All Patients &amp; all encounters</t>
+  </si>
+  <si>
+    <t>All Patients &amp; relevant encounters</t>
+  </si>
+  <si>
+    <t>Users &amp; all encounters</t>
+  </si>
+  <si>
+    <t>Users &amp; relevant encounters</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -63,13 +119,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -107,7 +171,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -141,6 +205,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -175,9 +240,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -350,75 +416,54 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="28.88671875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>group</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>mean</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>variance</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>sd</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>se</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>ci_norm_lower</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>ci_norm_upper</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>ci_basic_lower</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>ci_basic_upper</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>ci_perc_lower</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>ci_perc_upper</t>
-        </is>
+    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>All Patients &amp; all encounters</t>
-        </is>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>11</v>
       </c>
       <c r="B2">
-        <v>39.004</v>
+        <v>39.003999999999998</v>
       </c>
       <c r="C2">
         <v>0.06</v>
@@ -427,72 +472,68 @@
         <v>0.245</v>
       </c>
       <c r="E2">
-        <v>0.008</v>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="F2">
         <v>38.558</v>
       </c>
       <c r="G2">
-        <v>39.518</v>
+        <v>39.518000000000001</v>
       </c>
       <c r="H2">
-        <v>38.546</v>
+        <v>38.545999999999999</v>
       </c>
       <c r="I2">
-        <v>39.513</v>
+        <v>39.512999999999998</v>
       </c>
       <c r="J2">
-        <v>38.529</v>
+        <v>38.529000000000003</v>
       </c>
       <c r="K2">
-        <v>39.496</v>
+        <v>39.496000000000002</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>All Patients &amp; relevant encounters</t>
-        </is>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>12</v>
       </c>
       <c r="B3">
-        <v>23.049</v>
+        <v>23.048999999999999</v>
       </c>
       <c r="C3">
-        <v>0.023</v>
+        <v>2.3E-2</v>
       </c>
       <c r="D3">
         <v>0.152</v>
       </c>
       <c r="E3">
-        <v>0.005</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="F3">
         <v>22.753</v>
       </c>
       <c r="G3">
-        <v>23.351</v>
+        <v>23.350999999999999</v>
       </c>
       <c r="H3">
-        <v>22.752</v>
+        <v>22.751999999999999</v>
       </c>
       <c r="I3">
         <v>23.349</v>
       </c>
       <c r="J3">
-        <v>22.752</v>
+        <v>22.751999999999999</v>
       </c>
       <c r="K3">
         <v>23.349</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Users &amp; all encounters</t>
-        </is>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>13</v>
       </c>
       <c r="B4">
-        <v>40.011</v>
+        <v>40.011000000000003</v>
       </c>
       <c r="C4">
         <v>0.06</v>
@@ -501,44 +542,42 @@
         <v>0.246</v>
       </c>
       <c r="E4">
-        <v>0.008</v>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="F4">
-        <v>39.535</v>
+        <v>39.534999999999997</v>
       </c>
       <c r="G4">
-        <v>40.499</v>
+        <v>40.499000000000002</v>
       </c>
       <c r="H4">
-        <v>39.521</v>
+        <v>39.521000000000001</v>
       </c>
       <c r="I4">
-        <v>40.576</v>
+        <v>40.576000000000001</v>
       </c>
       <c r="J4">
-        <v>39.452</v>
+        <v>39.451999999999998</v>
       </c>
       <c r="K4">
         <v>40.506</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Users &amp; relevant encounters</t>
-        </is>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>14</v>
       </c>
       <c r="B5">
         <v>23.706</v>
       </c>
       <c r="C5">
-        <v>0.024</v>
+        <v>2.4E-2</v>
       </c>
       <c r="D5">
         <v>0.154</v>
       </c>
       <c r="E5">
-        <v>0.005</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="F5">
         <v>23.407</v>
@@ -547,13 +586,13 @@
         <v>24.009</v>
       </c>
       <c r="H5">
-        <v>23.388</v>
+        <v>23.388000000000002</v>
       </c>
       <c r="I5">
-        <v>24.005</v>
+        <v>24.004999999999999</v>
       </c>
       <c r="J5">
-        <v>23.409</v>
+        <v>23.408999999999999</v>
       </c>
       <c r="K5">
         <v>24.026</v>

--- a/CPRD Raw Analysis/Results/Overall/overall_combined_bootstrap_summary_encounters_SOURCE.xlsx
+++ b/CPRD Raw Analysis/Results/Overall/overall_combined_bootstrap_summary_encounters_SOURCE.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -418,7 +418,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>39.004</v>
+        <v>39</v>
       </c>
       <c r="C2">
         <v>0.06</v>
@@ -430,133 +430,59 @@
         <v>0.008</v>
       </c>
       <c r="F2">
-        <v>38.558</v>
+        <v>38.554</v>
       </c>
       <c r="G2">
-        <v>39.518</v>
+        <v>39.514</v>
       </c>
       <c r="H2">
-        <v>38.546</v>
+        <v>38.541</v>
       </c>
       <c r="I2">
-        <v>39.513</v>
+        <v>39.508</v>
       </c>
       <c r="J2">
-        <v>38.529</v>
+        <v>38.527</v>
       </c>
       <c r="K2">
-        <v>39.496</v>
+        <v>39.493</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>All Patients &amp; relevant encounters</t>
+          <t>Users &amp; all encounters</t>
         </is>
       </c>
       <c r="B3">
-        <v>23.049</v>
+        <v>39.992</v>
       </c>
       <c r="C3">
-        <v>0.023</v>
+        <v>0.067</v>
       </c>
       <c r="D3">
-        <v>0.152</v>
+        <v>0.259</v>
       </c>
       <c r="E3">
-        <v>0.005</v>
+        <v>0.008</v>
       </c>
       <c r="F3">
-        <v>22.753</v>
+        <v>39.498</v>
       </c>
       <c r="G3">
-        <v>23.351</v>
+        <v>40.513</v>
       </c>
       <c r="H3">
-        <v>22.752</v>
+        <v>39.517</v>
       </c>
       <c r="I3">
-        <v>23.349</v>
+        <v>40.523</v>
       </c>
       <c r="J3">
-        <v>22.752</v>
+        <v>39.475</v>
       </c>
       <c r="K3">
-        <v>23.349</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Users &amp; all encounters</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>40.011</v>
-      </c>
-      <c r="C4">
-        <v>0.06</v>
-      </c>
-      <c r="D4">
-        <v>0.246</v>
-      </c>
-      <c r="E4">
-        <v>0.008</v>
-      </c>
-      <c r="F4">
-        <v>39.535</v>
-      </c>
-      <c r="G4">
-        <v>40.499</v>
-      </c>
-      <c r="H4">
-        <v>39.521</v>
-      </c>
-      <c r="I4">
-        <v>40.576</v>
-      </c>
-      <c r="J4">
-        <v>39.452</v>
-      </c>
-      <c r="K4">
-        <v>40.506</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Users &amp; relevant encounters</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>23.706</v>
-      </c>
-      <c r="C5">
-        <v>0.024</v>
-      </c>
-      <c r="D5">
-        <v>0.154</v>
-      </c>
-      <c r="E5">
-        <v>0.005</v>
-      </c>
-      <c r="F5">
-        <v>23.407</v>
-      </c>
-      <c r="G5">
-        <v>24.009</v>
-      </c>
-      <c r="H5">
-        <v>23.388</v>
-      </c>
-      <c r="I5">
-        <v>24.005</v>
-      </c>
-      <c r="J5">
-        <v>23.409</v>
-      </c>
-      <c r="K5">
-        <v>24.026</v>
+        <v>40.481</v>
       </c>
     </row>
   </sheetData>
